--- a/20260804_従業員管理_04_検証データセット.xlsx
+++ b/20260804_従業員管理_04_検証データセット.xlsx
@@ -22,6 +22,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_勤務データ_2026-05_全稼働日" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_勤務データ_2026-06_月中改定検証" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_移行前後_突合テンプレート" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_前回取込_設定_差分確認用" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_前回取込_実績_差分確認用" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7088,6 +7090,372 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11.2" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="11.2" customWidth="1" min="3" max="3"/>
+    <col width="9.600000000000001" customWidth="1" min="4" max="4"/>
+    <col width="9.600000000000001" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>従業員コード</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>前回</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>単位給与額</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>330000</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>350000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>みなし残業時間</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>単位給与額</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>320000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>所定労働時間</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>単位給与額</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>360000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>380000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11.2" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9.600000000000001" customWidth="1" min="4" max="4"/>
+    <col width="9.600000000000001" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>従業員コード</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>前回</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>総労働時間</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>EMP-001</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>給与</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>370000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>378672</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>給与</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>320000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>337000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>EMP-002</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>交通費</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>EMP-003</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>総労働時間</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/20260804_従業員管理_04_検証データセット.xlsx
+++ b/20260804_従業員管理_04_検証データセット.xlsx
@@ -24,6 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_移行前後_突合テンプレート" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_前回取込_設定_差分確認用" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_前回取込_実績_差分確認用" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_列マッピング表_テンプレ_sample" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7456,6 +7457,268 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11.2" customWidth="1" min="2" max="2"/>
+    <col width="11.2" customWidth="1" min="3" max="3"/>
+    <col width="11.2" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>取込</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CSV列名</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>反映先テーブル</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ラクミー列名</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>従業員コード</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>従業員</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>従業員コード</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>従業員</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>雇用区分</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>従業員</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>雇用区分</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>給与単位</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>給与単位</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>単位給与額</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>単位給与額</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>交通費単位</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>交通費単位</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>単位交通費</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>単位交通費</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>所定労働時間</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>所定労働時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>みなし残業時間</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>みなし残業時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>所属店舗コード</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>従業員</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>所属店舗</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
